--- a/ModelShield_TP_FN_PickleBall(Malicious).xlsx
+++ b/ModelShield_TP_FN_PickleBall(Malicious).xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ML_Project_2026\ACSAC\2.final_artifacts\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A6D9D5-D6AE-4993-B2A7-2A43264F6C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37584BE7-C3E6-468B-B448-A77304039930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCA21FD0-36A2-4902-8EAD-6747F24F8CD8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="PickleBall (84 Malicious)" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
